--- a/org/sabae-jinko.files/R8jinko3.xlsx
+++ b/org/sabae-jinko.files/R8jinko3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs\Docs_2025\Gyosei\Gyosei\統計\06ホームページ\R8.3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs\Docs_2026\DX\34_統計\06_ホームページ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CCB13-3BD9-494B-97DD-BC9A8ACA11CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194D8C74-6E1C-41D3-B932-4B48FE16C5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6488ABE7-C9EC-42D5-B966-3DD9CA3CA1F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6488ABE7-C9EC-42D5-B966-3DD9CA3CA1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="R8.3.1" sheetId="36" r:id="rId1"/>
@@ -1822,16 +1822,16 @@
         <v>7</v>
       </c>
       <c r="J6" s="14">
-        <v>3861</v>
+        <v>3751</v>
       </c>
       <c r="K6" s="15">
-        <v>5004</v>
+        <v>4831</v>
       </c>
       <c r="L6" s="15">
-        <v>5098</v>
+        <v>4939</v>
       </c>
       <c r="M6" s="16">
-        <v>10102</v>
+        <v>9770</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -1860,16 +1860,16 @@
         <v>9</v>
       </c>
       <c r="J7" s="19">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K7" s="19">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L7" s="19">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M7" s="16">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -1888,7 +1888,7 @@
         <v>11</v>
       </c>
       <c r="J8" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
@@ -1916,16 +1916,16 @@
         <v>12</v>
       </c>
       <c r="J9" s="16">
-        <v>4047</v>
+        <v>3930</v>
       </c>
       <c r="K9" s="16">
-        <v>5118</v>
+        <v>4939</v>
       </c>
       <c r="L9" s="16">
-        <v>5194</v>
+        <v>5032</v>
       </c>
       <c r="M9" s="16">
-        <v>10312</v>
+        <v>9971</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -2062,16 +2062,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="14">
-        <v>5971</v>
+        <v>6081</v>
       </c>
       <c r="D14" s="15">
-        <v>7288</v>
+        <v>7461</v>
       </c>
       <c r="E14" s="15">
-        <v>7695</v>
+        <v>7854</v>
       </c>
       <c r="F14" s="16">
-        <v>14983</v>
+        <v>15315</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="17" t="s">
@@ -2098,16 +2098,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="19">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D15" s="19">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E15" s="19">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F15" s="16">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>16</v>
@@ -2135,7 +2135,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="19">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -2158,16 +2158,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="16">
-        <v>6297</v>
+        <v>6414</v>
       </c>
       <c r="D17" s="16">
-        <v>7534</v>
+        <v>7713</v>
       </c>
       <c r="E17" s="16">
-        <v>7861</v>
+        <v>8023</v>
       </c>
       <c r="F17" s="16">
-        <v>15395</v>
+        <v>15736</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="17" t="s">
@@ -5626,16 +5626,16 @@
         <v>7</v>
       </c>
       <c r="J6" s="14">
-        <v>3858</v>
+        <v>3747</v>
       </c>
       <c r="K6" s="15">
-        <v>5005</v>
+        <v>4831</v>
       </c>
       <c r="L6" s="15">
-        <v>5090</v>
+        <v>4931</v>
       </c>
       <c r="M6" s="16">
-        <v>10095</v>
+        <v>9762</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -5664,16 +5664,16 @@
         <v>9</v>
       </c>
       <c r="J7" s="19">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K7" s="19">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L7" s="19">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M7" s="16">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -5692,7 +5692,7 @@
         <v>11</v>
       </c>
       <c r="J8" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
@@ -5720,16 +5720,16 @@
         <v>12</v>
       </c>
       <c r="J9" s="16">
-        <v>4046</v>
+        <v>3927</v>
       </c>
       <c r="K9" s="16">
-        <v>5120</v>
+        <v>4939</v>
       </c>
       <c r="L9" s="16">
-        <v>5187</v>
+        <v>5025</v>
       </c>
       <c r="M9" s="16">
-        <v>10307</v>
+        <v>9964</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18.899999999999999" customHeight="1">
@@ -5866,16 +5866,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="14">
-        <v>5961</v>
+        <v>6072</v>
       </c>
       <c r="D14" s="15">
-        <v>7300</v>
+        <v>7474</v>
       </c>
       <c r="E14" s="15">
-        <v>7690</v>
+        <v>7849</v>
       </c>
       <c r="F14" s="16">
-        <v>14990</v>
+        <v>15323</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="17" t="s">
@@ -5902,16 +5902,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="19">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D15" s="19">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E15" s="19">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F15" s="16">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>16</v>
@@ -5939,7 +5939,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="19">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -5962,16 +5962,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="16">
-        <v>6285</v>
+        <v>6404</v>
       </c>
       <c r="D17" s="16">
-        <v>7551</v>
+        <v>7732</v>
       </c>
       <c r="E17" s="16">
-        <v>7850</v>
+        <v>8012</v>
       </c>
       <c r="F17" s="16">
-        <v>15401</v>
+        <v>15744</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="17" t="s">
